--- a/artfynd/A 61826-2022 artfynd.xlsx
+++ b/artfynd/A 61826-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61826-2022 artfynd.xlsx
+++ b/artfynd/A 61826-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14928749</v>
+        <v>1978168</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ekorrsele: Brännheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700452.8733398881</v>
+        <v>700401</v>
       </c>
       <c r="R2" t="n">
-        <v>7154382.999332896</v>
+        <v>7154455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2011-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,69 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Sporrong, Andreas Garpebring, Sören Uppsäll</t>
+          <t>Sören Uppsäll, Henrik Sporrong, Per-anders Blomqvist, Andreas Garpebring, Per Nihlén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106542617</v>
+        <v>2058208</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+          <t>Ekorrsele: Brännheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700459.6072322677</v>
+        <v>700401</v>
       </c>
       <c r="R3" t="n">
-        <v>7154386.039070019</v>
+        <v>7154455</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +861,245 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>kolad stubbe</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll, Henrik Sporrong, Andreas Garpebring, Per Nihlén, Per-anders Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14928749</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ekorrsele: Brännheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>700453</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7154383</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-10-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-10-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Sporrong, Andreas Garpebring, Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106542617</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700460</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7154386</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61826-2022 artfynd.xlsx
+++ b/artfynd/A 61826-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1978168</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2058208</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14928749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106542617</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>